--- a/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
+++ b/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,15 @@
       <sz val="14"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
     <font>
@@ -54,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,34 +69,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,203 +467,211 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Filters - Questions for Branko (from the engineering plan) - 2026-07-30</t>
+          <t>Filters - Questions for Branko - 2026-07-30 (revised 2026-07-31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Revised 2026-07-31 - this version replaces the 2026-07-30 draft, which was never sent. Two of the earlier questions (and a naming question inside one of them) have been removed, because your latest written requirements for the filters (version 1.6, updated 28 July) already answer them. Two new items have been added: sorting, and which details the new in-page search box looks at.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>What happens now</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>The question</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Opening someone else's filtered link</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>A teammate can send a link that opens the Work Orders page with certain filters already picked. Engineering is building it so the link is a TEMPORARY view: it never replaces the filters you saved for yourself, and a small "back to my saved filters" option brings your own filters back. One sentence in the written description says the opposite (the link's filters would become your saved ones).</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>When I open someone's filtered link, should it show their view temporarily and leave my saved filters untouched, or replace my saved filters?</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>A) Show their view temporarily and leave MY saved filters untouched (what engineering is building - and what you reportedly agreed in the page comments).
-B) Replace my saved filters with the link's filters.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The "Imported" status works alone</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Imported work orders live in a separate list behind the scenes. Engineering is building the Imported choice so it works ALONE: when you pick Imported, the other filter buttons (Customer, Lead Technician, Service Advisor, Asset on site) grey out and cannot be combined with it. The written description lists Imported as a normal status like any other.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Should picking "Imported" work alone and grey out the other filters?</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>A) Yes - Imported works alone (what engineering is building; combining it is not technically possible today).
-B) No - I expected it to combine like the other statuses (this would need extra engineering work).</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Mobile: single filter windows - instant or with an Apply button</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>On a phone, tapping one filter button opens a small window from the bottom. The design pictures show an "Apply filter" button in that window; the engineering plan makes single-filter windows apply INSTANTLY as you tick (no button) - only the combined "All Filters" window keeps an "Apply filters" button.</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>In the single-filter window on a phone, should choices apply instantly as you tick, or only after tapping an "Apply filter" button?</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>A) Instantly as you tick, no Apply button (the engineering plan's way).
 B) Only after tapping an "Apply filter" button (as the design pictures show).</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Which tab opens first</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Engineering decided that the very FIRST time someone opens the redesigned Work Orders page, the ESTIMATES tab is selected (even though "All" is the first tab in the row). After that, the page always reopens on the tab you used last. This was decided for speed reasons and is not written in the product description.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Engineering decided that the very FIRST time someone opens the redesigned Work Orders page, the ESTIMATES tab is selected (even though "All" is the first tab in the row). After that, the page always reopens on the tab you used last. This was decided for speed reasons and is not written down anywhere.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Is Estimates the right tab to open first for a brand-new visit?</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>A) Yes - Estimates first is fine.
 B) No - it should open on All (please note: engineering chose Estimates to keep the heaviest list off the landing page; picking B needs a talk with them).</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>The Parts "Vendors" page filters</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>The written description lists a Vendors view among the Parts pages that get filters, but engineering could not find a design picture for it and will not build its filters until a design exists. They have requested the design.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Please confirm the Vendors page IS meant to get filters, and have the design added - or tell us it is out of scope.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>A) Vendors gets filters - design coming.
 B) Vendors is out of scope for now.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sorting the Work Orders list</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>The design pictures include a sorting panel for the Work Orders list: you pick a column (for example Status, or WO Number), you pick Ascending or Descending, there is an "Add Sort" option that lets you sort by a second column at the same time, and a "Delete sort" option to remove one. The written description does not describe any sorting control at all, so we have no tests for sorting - not one. The sorting pictures are also marked "Work In Progress", which is why we are asking rather than assuming. A sort button also shows on the phone version of the Work Orders page, and on two report pages (Notes and Reminders).</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Is sorting part of this project? If yes, should it allow more than one sort level at a time, and are the sort buttons on the phone version and on those two report pages included too?</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>A) Yes - sorting is in scope for this project, including more than one sort level at a time (please add it to the written description so we can write the tests).
+B) Yes, but single-level only - one column at a time, no "Add Sort".
+C) No - sorting is not part of this project (the design pictures are exploration only).</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Which details the new in-page search box looks at</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Each list page is getting its own small search box that narrows the list as you type. The written description says each page keeps looking at the same details it already searches today, and it also says the list of those details is still to come from engineering - so right now nobody has written down what each page's search box actually looks at (on Work Orders, for example: the order number? the customer name? the unit number?). Until that list exists we cannot write or run a test that proves the search box looks at the right details - we can only check that typing narrows the list.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Please have that list written down per page and shared with us - or tell us to accept "whatever each page's search finds today" as correct.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>A) The list of searchable details will be written down and shared (please say roughly when).
+B) Accept whatever each page's search finds today - we will only test that typing narrows the list, not which details it matches.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>The updated requirements page (a request, not a choice)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>The engineering plan tells us the requirements page for the filters has newer content than the copy we have. The newer version also covers the Parts page filters, the Reports page filters, a new date-range filter, the new in-page search box, and a change to how the top search bar works. Our copy is the original version.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>The requirements page has newer content than what we have - please export/share the latest version (the same way as before), so we can bring all the tests in line with it. This also covers the updated write-up we asked for on July 17 - it looks like it already exists.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>A) Shared - here is the latest version (sent along with these answers).
-B) It will follow shortly (please say when).</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Your latest written description (a request, not a choice)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>We now have your latest written description of the filters (version 1.6, updated 28 July) and we are bringing all the tests in line with it. Our earlier copy was the very first version, so for a while we were testing against out-of-date wording without knowing it.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Please confirm version 1.6 is the current one, and let us know each time you change it, so we can re-check the tests straight away.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>A) Yes - version 1.6 is current, and I will let you know whenever I update it.
+B) There is something newer than version 1.6 (please share it).</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -678,164 +684,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>QA-ONLY - do not send this sheet to the PO. TestRail C-ids from build/filters/testrail-id-map.csv (Rule 8); link https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>QA-ONLY - do not send this sheet to the PO. REVISED 2026-07-31 against the current Filters spec v1.6 (Confluence page 572030978, Confluence version 12, body version 1.6, updated 2026-07-28 by Branko Cicovic; pulled live 2026-07-31, verbatim body in spec-current-2026-07-31/Filters-spec-current.md). SUPERSEDES the 2026-07-30 version, which was NOT sent: 3 questions withdrawn (already answered by spec v1.4/v1.5 - see the WITHDRAWN rows), 2 added (sorting scope; the S13-R23 searchable-field list), reader-facing questions renumbered 1-6, old Q6 (spec-export request) reframed to confirm-current + notify-us because we pulled v1.6 ourselves. TestRail C-ids from build/filters/testrail-id-map.csv (Rule 8); link https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Q#</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Affected internal case IDs (TestRail C-id)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Source refs</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>What each answer resolves to</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>FLT-URL-02 (C29618)
-FLT-URL-05 (new, no C-ID yet)
-FLT-PSRCH-04 (new, no C-ID yet)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Source: tech-plan-2026-07-29/Questions-for-Branko-dev.md Q2 = TECH-PLAN-DELTAS conflict C1 (tech plan G7: shared-link view is runtime-only, never persisted, with a 'back to my saved filters' affordance; spec sentence says link state persists). Plan cites Branko's page-comment agreement - unconfirmed.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; FLT-URL-02 gains the runtime-only + revert affordance expected; author FLT-URL-05/FLT-PSRCH-04 as staged. B -&gt; keep the persisting-link expected; engineering must change the build. Verify LIVE at VIU either way.</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>FLT-MOB-04 (C29624)
+FLT-MOB-02 (C29622)
+FLT-MOB-03 (C29623)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Source: tech-plan-2026-07-29/Questions-for-Branko-dev.md Q4 = TECH-PLAN-DELTAS conflict C4 (tech plan D15: single-filter bottom sheets apply in real time, no Apply button; design pictures 11884:21065/21271 show 'Apply filter' in the single-filter sheet). Spec S12-R2 (unchanged since V1.0) says mobile behaves identically to desktop; desktop S2-R6 is real-time. Independently re-raised by Ahtesham 2026-07-31 (VERIFICATION.md CONFLICT 2).</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; reword FLT-MOB-04 to instant-apply, no button. B -&gt; case stands as designed (Apply button). Either way FLT-MOB-02/03 keep the combined-sheet Apply button (design 11884:13689 + D15 = IN) and all three get the same 'confirm live which pattern ships' note (FIX-PLAN F2). Verify LIVE at VIU.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FLT-STAT-03 (C29562)
-FLT-STAT-07 (new, no C-ID yet)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Source: Questions-for-Branko-dev.md Q3 = conflict C2 (tech plan G1: 'Imported' is EXCLUSIVE - selecting it disables the other four chips; spec lists Imported as a normal status value).</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; FLT-STAT-03 gains the exclusivity expected + FLT-STAT-07 (greyed-out chips) goes in. B -&gt; cases keep combinable-Imported and engineering needs extra work. Verify LIVE at VIU.</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>FLT-TAB-06 (C38876)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Source: Questions-for-Branko-dev.md Q5 = conflict C5 (tech plan D10: first-visit default tab = Estimates for load reasons; not in the spec - still absent in v1.6).</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; FLT-TAB-06 stands as pushed (Estimates-first + last-tab-remembered). B -&gt; reword to All-first; engineering discussion needed first.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>FLT-MOB-04 (C29624)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Source: Questions-for-Branko-dev.md Q4 = conflict C4 (tech plan D15: single-filter bottom sheets apply in real time, no Apply button; the design pictures show 'Apply filter' in the single-filter sheet).</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; reword FLT-MOB-04 to instant-apply, no button. B -&gt; case stands as designed (Apply button). Verify LIVE at VIU.</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>no case exists (FLT-PARTS-08 was proposed 2026-07-30 and is NOT in the current id-map - the Parts area was consolidated 2026-07-31 to FLT-PARTS-01/09/11/12, all blank C-ids)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Source: Questions-for-Branko-dev.md Q6 = conflict C7 (spec lists a Parts Vendors view for filters; no design exists; engineering will not build until a design lands - they requested it).</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author the Vendors filter case(s) once the design arrives. B -&gt; mark Vendors filters out of scope; no case.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>FLT-TAB-06 (new, no C-ID yet)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Source: Questions-for-Branko-dev.md Q5 = conflict C5 (tech plan D10: first-visit default tab = Estimates for load reasons; not in the spec).</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; author FLT-TAB-06 with Estimates-first + last-tab-remembered. B -&gt; All-first; engineering discussion needed before the case is authored.</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>NEW AREA - no cases exist at all (no FLT-SORT area; zero sorting cases in the 110-case active suite)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Source: design-2026-07-31/DESIGN-NOTES.md 5.1 - Figma section 'Sorting (Work In Progress)', boards 11985:9686 / 11985:10428 / 11985:11259 / 11985:13334 (Sort dropdown = field box [Status, WO Number] + direction box [Ascending] + 'Add Sort' + 'Delete sort'; step 4 shows TWO stacked sort rows = multi-level). Sort button also on final mobile boards 11884:20807 / 11884:15901 / 12867:12201 and on the Reports Notes + Reminders boards. Spec v1.6 mentions sorting ONCE, in passing, at S13-R14 ('The search query ... survives sorting, pagination...') - there is NO sorting requirement anywhere in the spec. 4 of the 4 sorting boards are still un-rendered (Figma image endpoint rate-limited; Rule 35 queue design-2026-07-31/PENDING-FIGMA-FETCH.md still OPEN) - the panel is described from its own text/layer names, not from a picture.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author a new FLT-SORT area (single-level + multi-level add/remove + direction + mobile sort button + the 2 Reports surfaces) AFTER Branko adds sorting to the spec; needs add_case authorization. B -&gt; author single-level only; no 'Add Sort' case. C -&gt; no cases; record sorting as out of scope in PROJECT-STATE + coverage-matrix so the design boards are never mistaken for scope. Do NOT author before the answer (Rule 1: designs marked Work In Progress are not a spec).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FLT-PARTS-08 (new, no C-ID yet)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Source: Questions-for-Branko-dev.md Q6 = conflict C7 (spec lists a Parts Vendors view for filters; no design exists; engineering will not build until a design lands - they requested it).</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>A -&gt; keep/author the Vendors filter case(s) once the design arrives. B -&gt; mark Vendors filters out of scope; no case.</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>FLT-PSRCH-01 (C38883)
+FLT-PSRCH-06 (C38891)
+plus the ~20 un-authored Story-13 cases</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Source: spec v1.6 S13-R23, verbatim: "Each table searches the fields its existing search endpoint already covers today... Pending: the per-table list of fields currently covered, from engineering. Until it exists the searchable set is undocumented and QA has no baseline to test against... Five of the surfaces listed under S14-R6 (Customer Contacts, Customer Assets, Customer Fees &amp; Discounts, Administration Locations, Administration Fees &amp; Discounts) narrow rows already loaded in the browser rather than querying an endpoint..." Confirmed STILL OPEN in v1.6 (spec-current file line 563; SPEC-DIFF 4b Group C; VERIFICATION 'Blocked by the spec itself').</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; on receipt of the field list, author per-page search-field cases (currently un-authorable). B -&gt; keep coverage at 'typing narrows the list' only (FLT-PSRCH-01/06) and record in the coverage-matrix that per-field matching is deliberately untested by PO ruling. Either way the ~20 remaining Story-13 gaps (component states, 300ms/350ms debounce, tab scoping, retention, mobile mechanics, negatives) are NOT blocked by this and still need authoring authorization.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>whole suite (122 authored; 79 in TestRail C29557-C29635 + 43 pending add_case)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Source: Questions-for-Branko-dev.md Q7 = conflict C9 (spec drift: the Confluence Filters page is at v1.3 - Parts/Reports filters, date-range filter, in-page Search box ~23 requirements, top-nav search change; our ingested copy is v1.0). Also settles C6/C8 (page-search ownership -&gt; FLT-SRCH-01..09 transfer/retire; query-per-tab).</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>On receipt of the v1.3 export -&gt; run SPEC-RELEVANCE-RECONCILIATION + build-accurate wording over the whole suite (Rule 11 ask first), then the authorized push. Until then the 43 new Parts/Reports/page-search cases stay design-only VIU-Pending.</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>whole suite (110 active authored; 94 live in TestRail, 16 blank C-ids)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Source: Questions-for-Branko-dev.md Q7 = conflict C9 (spec drift). Now largely self-resolved: we pulled v1.6 live from Confluence 2026-07-31 (page 572030978, Confluence v12) instead of waiting for an export - 8 Confluence versions / 5 spec minor versions behind, 49 requirements added, 0 removed, 4 changed (SPEC-DIFF 1/2). Remaining ask = confirm-current + notify-on-change (Standing Rule 23 re-pull is now the standing habit).</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; proceed with the v1.6 reconciliation already in flight (re-ingest requirements.md, FIX-PLAN F1-F7, then the ~28 new-case authoring pass, then run 352 refresh). B -&gt; re-pull the newer version first and re-diff before any push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>W1 - WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>FLT-URL-05 (C38879)
+FLT-URL-02 (C29618)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>WITHDRAWN - answered by spec v1.6 (S11-R6, added v1.4 / Confluence v9, 2026-07-27). Was Q1 of the 2026-07-30 sheet (= Questions-for-Branko-dev.md Q2 / deltas C1). VERBATIM: "Filter state arriving from a URL applies at runtime only. It never overwrites the user's saved filter state (S10-R2). Changes the user makes to filters while viewing a shared link are also not written back to their saved state: the entire visit is treated as a temporary view"</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Effective answer = option A (runtime-only; saved filters untouched; changes during the visit are not written back either). FLT-URL-05 already tests it clause-by-clause; only its refs/spec_ref are stale ('spec v1.3 export awaited') -&gt; re-point to S11-R6 (FIX-PLAN F4). Never sent to Branko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>W2 - WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>FLT-STAT-07 (C38877)
+FLT-STAT-03 (C29562)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>WITHDRAWN - answered by spec v1.6 (S2-R7 + S2-N4, added v1.4 / Confluence v9, 2026-07-27). Was Q2 of the 2026-07-30 sheet (= Questions-for-Branko-dev.md Q3 / deltas C2). VERBATIM S2-R7: "Imported is an exception to S2-R2 and cannot be combined with anything else. Imported work orders come from a different data source rather than being a status of the existing records, so selecting Imported switches the list to the imported records and disables the other filter chips while it is active. Deselecting Imported returns the list and re-enables the other chips. This is current production behaviour and is unchanged by this work" | VERBATIM S2-N4: "Selecting Imported alongside another status, customer, technician, advisor or asset filter is not a supported combination and is prevented by S2-R7 rather than returning an empty result"</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Effective answer = option A (Imported works alone; other chips disabled while active; deselecting re-enables them). FLT-STAT-07 already covers S2-R7 + S2-N4 fully; only its refs/spec_ref + its 'PENDING BRANKO' note are stale (FIX-PLAN F3). Never sent to Branko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>W3 - WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FLT-URL-05 (C38879)
+FLT-URL-06 (new, no C-ID yet)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>WITHDRAWN - answered by spec v1.6 (S11-R7; CTA renamed in v1.5 / Confluence v10, 2026-07-27). Was the naming question INSIDE Q1 of the 2026-07-30 sheet ('a small "back to my saved filters" option'). VERBATIM: "While viewing filter state that arrived from a URL, a "Back to my view" action is available. It discards the shared view and restores the user's own saved filters. It also clears any active search query, because the query is not part of saved state and there is nothing to restore it to. The label is deliberately "my view" rather than "my filters", since the action affects both filters and search"</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Ratified label = 'Back to my view' (not 'back to my saved filters'). Use it in FLT-URL-05 per Rule 9 and add the untested 'it also clears any active search query' clause (FIX-PLAN F5); the negative S11-N3 ('not shown when viewing your own state') still needs a NEW case (FIX-PLAN F6). Never sent to Branko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Already resolved - NOT asked</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>FLT-TAB-02 (C29609)
+FLT-TAB-03 (C29610)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Status chip on Estimates/Completed tabs (Questions-for-Branko-dev.md Q1 / delta C3) - RESOLVED by user ruling 2026-07-30: the tech plan's 'hidden' and Branko's earlier 'greyed-out/disabled' describe the SAME behavior. Note 2026-07-31: spec v1.6 still says 'hidden'/'not shown' in S9-R2, S9-R3, S2-N1, S2-N2, S1-N1 and section 4 Key Decisions - text unchanged since V1.0.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Cases stand as pushed - no case change, no TestRail write. The PRD-alignment ask for Branko is FIX-PLAN B1, deliberately NOT added to this sheet; it does not reopen the ruling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Already resolved - NOT asked</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>FLT-SRCH-01..09 (no C-ids; none in TestRail)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Page-search 'spotlight/palette' ownership - already put to Branko as Question 6 of PO-Questions-Branko-PartsReports-2026-07-27.md ('The pop-up search box'); not duplicated here. SPEC-DIFF section 4 Group D is strong new evidence they are Global Search v2, not Filters Story 13.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Per user ruling 2026-07-31 the nine cases are NOT to be deleted unless Branko confirms Global-Search-only ownership. His answer decides move-vs-keep.</t>
         </is>
       </c>
     </row>

--- a/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
+++ b/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -467,14 +467,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Filters - Questions for Branko - 2026-07-30 (revised 2026-07-31)</t>
+          <t>Filters - Questions for Branko - 2026-07-30 (revised again 2026-07-31) - 8 questions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Revised 2026-07-31 - this version replaces the 2026-07-30 draft, which was never sent. Two of the earlier questions (and a naming question inside one of them) have been removed, because your latest written requirements for the filters (version 1.6, updated 28 July) already answer them. Two new items have been added: sorting, and which details the new in-page search box looks at.</t>
+          <t>Revised again 2026-07-31 - 8 questions in total. FIRST revision (2026-07-31): replaced the 2026-07-30 draft, which was never sent; two earlier questions (and a naming question inside one of them) were removed because your latest written requirements for the filters (version 1.6, updated 28 July) already answer them, and two items were added (sorting; which details the new in-page search box looks at). SECOND revision (2026-07-31): two more questions added (now Questions 7 and 8) after reading your answers of 27 July on the Parts, Reports and page-search sheet - one to confirm which search box your answer covers, one about six filter buttons the design pictures never show opened. Question 4 (sorting) has also been made more specific now that we have been through the sorting pictures in full. Total: 8 questions.</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>The design pictures include a sorting panel for the Work Orders list: you pick a column (for example Status, or WO Number), you pick Ascending or Descending, there is an "Add Sort" option that lets you sort by a second column at the same time, and a "Delete sort" option to remove one. The written description does not describe any sorting control at all, so we have no tests for sorting - not one. The sorting pictures are also marked "Work In Progress", which is why we are asking rather than assuming. A sort button also shows on the phone version of the Work Orders page, and on two report pages (Notes and Reminders).</t>
+          <t>The design pictures include a sorting panel for the Work Orders list: you pick a column (for example Status, or WO Number), there is a direction box next to it, there is an "Add Sort" option that lets you sort by a second column at the same time, and a "Delete sort" option to remove sorting. The written description does not describe any sorting control at all, so we have no tests for sorting - not one. The sorting pictures are also marked "Work In Progress", which is why we are asking rather than assuming. A sort button also shows on the phone version of the Work Orders page, and on two report pages (Notes and Reminders). Two details we cannot work out from the pictures: (1) once two sorts have been added, the "Add Sort" option is no longer shown - only "Delete sort" is left - so we cannot tell whether two at a time is the intended maximum or simply as far as the picture was drawn; (2) every sort row reads "Ascending", no picture shows a way to switch it the other way round, and the sorted column heading carries no mark, so we cannot tell how someone reverses a sort or whether the sorted column should show any sign that it is sorted.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Is sorting part of this project? If yes, should it allow more than one sort level at a time, and are the sort buttons on the phone version and on those two report pages included too?</t>
+          <t>Is sorting part of this project? If yes: is two sorts at a time the intended maximum; how does someone reverse a sort so it runs the other way, and should the sorted column show a mark; and are the sort buttons on the phone version and on those two report pages included too?</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>A) Yes - sorting is in scope for this project, including more than one sort level at a time (please add it to the written description so we can write the tests).
+          <t>A) Yes - sorting is in scope for this project, including more than one sort level at a time (please add it to the written description, including the maximum number of sorts and how the direction is reversed, so we can write the tests).
 B) Yes, but single-level only - one column at a time, no "Add Sort".
 C) No - sorting is not part of this project (the design pictures are exploration only).</t>
         </is>
@@ -672,6 +672,61 @@
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>The search box on the page itself, versus the pop-up search</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>You told us the pop-up search box ("Search or ask a question") should be tested with the global search work, not here - so we have moved those tests out. But the written requirements for THIS project also describe a different search box: a small one that sits on the page's own toolbar. You type in it and the list below narrows, with no separate results window. We have tests written for that page toolbar search box here.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Is that search box on the page toolbar still part of this project?</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>A) Yes - the search box on the page toolbar stays in this project; only the pop-up search moves to the global search work.
+B) No - everything to do with searching moves to the global search work, including the search box on the page toolbar.
+Please note: if the answer is B, a sizeable set of tests we have already written moves out of this project, so we want to be sure before we move them.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Six of the newer filter buttons are never shown opened</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>You told us the filter behaviour and the filter types are fully shown in the design pictures. For one of them that is exactly right: the Parts "Part type" button is drawn opened, so we can see its choices (Core, Non Core, and a "Clear selection" option) - we have everything we need for that one. For six others the pictures only show the button sitting in the toolbar and never show it opened: Location, Transaction Type, Invoice Status, Type, User and Mention. We have now been through every one of the 85 design pictures, so there is no unopened picture left for us to find. That means a tester cannot tell what happens when one of those six is used - what choices it offers, or what picking one does to the list.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>For those six buttons, can we get a one or two line written description of each - what choices it offers, and what happens to the list when you pick one?</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>A) Yes - a short written description will be added for those six.
+B) No - treat the design pictures as the source, and ask me about each one as you come to it.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -684,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -696,10 +751,11 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>QA-ONLY - do not send this sheet to the PO. REVISED 2026-07-31 against the current Filters spec v1.6 (Confluence page 572030978, Confluence version 12, body version 1.6, updated 2026-07-28 by Branko Cicovic; pulled live 2026-07-31, verbatim body in spec-current-2026-07-31/Filters-spec-current.md). SUPERSEDES the 2026-07-30 version, which was NOT sent: 3 questions withdrawn (already answered by spec v1.4/v1.5 - see the WITHDRAWN rows), 2 added (sorting scope; the S13-R23 searchable-field list), reader-facing questions renumbered 1-6, old Q6 (spec-export request) reframed to confirm-current + notify-us because we pulled v1.6 ourselves. TestRail C-ids from build/filters/testrail-id-map.csv (Rule 8); link https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;</t>
-        </is>
-      </c>
-    </row>
+          <t>QA-ONLY - do not send this sheet to the PO. REVISED 2026-07-31 against the current Filters spec v1.6 (Confluence page 572030978, Confluence version 12, body version 1.6, updated 2026-07-28 by Branko Cicovic; pulled live 2026-07-31, verbatim body in spec-current-2026-07-31/Filters-spec-current.md). SUPERSEDES the 2026-07-30 version, which was NOT sent: 3 questions withdrawn (already answered by spec v1.4/v1.5 - see the WITHDRAWN rows), 2 added (sorting scope; the S13-R23 searchable-field list), reader-facing questions renumbered 1-6, old Q6 (spec-export request) reframed to confirm-current + notify-us because we pulled v1.6 ourselves. TestRail C-ids from build/filters/testrail-id-map.csv (Rule 8); link https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt; SECOND REVISION 2026-07-31: two questions ADDED (Q7, Q8) after ingesting Branko's 2026-07-27 answers to PO-Questions-Branko-PartsReports-2026-07-27 (ingested/analysed 2026-07-31 in branko-answers-2026-07-31/answers-ingested.md + DELTAS.md). Q7 = flag F2 (his Q6=A confirms the pop-up palette is Global Search, satisfying the user 2026-07-31 hold ruling, but his sentence 2 read literally would also descope Story 13 Page Search = 29 ratified requirements in v1.6 tested by 13 FLT-PSRCH cases). Q8 = flag F1 (his Q4 answered by pointer only; the 6 new filter types are enumerated nowhere in v1.6). Q1-Q6 unchanged and NOT renumbered. Total = 8 reader-facing questions. ZERO case edits, ZERO id-map/import writes, ZERO TestRail writes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -808,7 +864,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>A -&gt; author a new FLT-SORT area (single-level + multi-level add/remove + direction + mobile sort button + the 2 Reports surfaces) AFTER Branko adds sorting to the spec; needs add_case authorization. B -&gt; author single-level only; no 'Add Sort' case. C -&gt; no cases; record sorting as out of scope in PROJECT-STATE + coverage-matrix so the design boards are never mistaken for scope. Do NOT author before the answer (Rule 1: designs marked Work In Progress are not a spec).</t>
+          <t>A -&gt; author a new FLT-SORT area (single-level + multi-level add/remove + direction + mobile sort button + the 2 Reports surfaces) AFTER Branko adds sorting to the spec; needs add_case authorization. B -&gt; author single-level only; no 'Add Sort' case. C -&gt; no cases; record sorting as out of scope in PROJECT-STATE + coverage-matrix so the design boards are never mistaken for scope. Do NOT author before the answer (Rule 1: designs marked Work In Progress are not a spec). SHARPENED 2026-07-31 (new design evidence, design-2026-07-31/DESIGN-NOTES.md commit 174b9d1 - the 4 sorting boards were read via the layer-tree endpoint and are STILL un-rendered as PNGs, Rule 35 queue still OPEN). (i) RETRACTION - our earlier read of sorting steps 1-2 is WITHDRAWN: there is NO sort control of any kind on step 1 (11985:9686) or step 2 (11985:10428); the earlier "sort arrow on the Status heading / sort button in the toolbar" reading was WRONG. The sort entry point FIRST appears on step 3 (11985:11259) as a Switch-vertical (up/down arrows) icon; step 2 only adds the field-picker menu listing "Status" and "WO Number". (ii) two-sort cap UNKNOWN (reader sub-point 1): "Add Sort" (plus icon) is present on step 3 (one row) but ABSENT on step 4 (11985:13334, two stacked rows) while panel-level "Delete sort" (trash icon) remains - either a deliberate 2-sort maximum or an unfinished board. (iii) direction + column indicator UNKNOWN (reader sub-point 2): the direction box reads "Ascending" in every row on every board - no Descending state anywhere, no drawn control to flip it, and no sort indicator on the sorted column heading. Both boxes are Input Textfield instances with a trailing chevron (= dropdowns), so a Descending option probably sits behind the field but is NEVER drawn. Consequence: even under answer A or B, the direction-toggle + column-indicator expectations stay un-authorable until his answer or a live build check lands (Rules 1/9/12).</t>
         </is>
       </c>
     </row>
@@ -861,112 +917,168 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>13 FLT-PSRCH cases: FLT-PSRCH-01 (C38883)
+FLT-PSRCH-02 (C38884)
+FLT-PSRCH-03 (C38886)
+FLT-PSRCH-04 (C38888)
+FLT-PSRCH-05 (C38889)
+FLT-PSRCH-06 (C38891)
+FLT-PSRCH-07 (C38893)
++ the 6 added 2026-07-31 by a sibling worker (FLT-PSRCH-08..13, blank C-ids, not yet in testrail-id-map.csv - RE-DERIVE from cases/*.json before quoting).
+Distinct from the 9 FLT-SRCH-01..09 palette cases (no C-ids), whose ownership his Q6=A already settles.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Source: branko-answers-2026-07-31/answers-ingested.md Q6 + DELTAS.md Q6 flag F2 / Verdict 2. His verbatim Q6 answer (2026-07-27): "A - Test it under Global Search, not here. This release only removes global search's page-filtering behaviour (Story 14). 'Ask a question' is not in this PRD's scope." Against spec v1.6 Story 13 = 29 ratified requirements (S13-R1..R29, incl. S13-R14, S13-R23) - the literal reading of sentence 2 CONTRADICTS the current spec. Rule 32 = newest source wins, so it cannot be inferred away; Rule 1 = do not proceed on an ambiguous scope.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>A (expected) -&gt; the 13 FLT-PSRCH cases STAY in Filters; only FLT-SRCH-01..09 move to Global Search (which his Q6 already licenses, satisfying the user 2026-07-31 hold ruling). B -&gt; a sizeable descope: all 13 FLT-PSRCH + the ~20 un-authored Story-13 gaps leave Filters for the Global Search project, and Story 13's 29 requirements come out of the Filters coverage-matrix. Do NOT delete/transfer/retire ANY page-search case before this answer (user ruling 2026-07-31 + Rule 6). The 2026-07-31 Ruthless Usefulness Audit CUT recommendation on the nine FLT-SRCH cases stays a RECOMMENDATION until this lands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>No case is blocked, but no case can be strengthened either - the six never-opened filter buttons are covered only at button-name/presence level by:
+FLT-PARTS-01, -09, -11, -12 (blank C-ids, never pushed)
+FLT-RPTS-01, -21, -22 (blank C-ids)
+FLT-RPTS-23 (C38882, live)
+Any per-type behavioural case (option list, apply-to-list, clearability, multi- vs single-select) is un-authorable for those six. Core / Non Core is deliberately NOT in this question - its options ARE pinned by the design, so its cases can be authored to Rule-9 wording now.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Source: branko-answers-2026-07-31/answers-ingested.md Q4 + DELTAS.md Q4 flag F1, NARROWED 2026-07-31 against the completed design read (design-2026-07-31/DESIGN-NOTES.md commit 174b9d1). His Q4 was answered by pointer only ("fully displayed in the design"). A text search across ALL 85 boards shows his claim holds for 1 of the 7 named types and fails for the other 6: Core / Non Core = YES, board "Part type" 11902:9973 is an OPEN dropdown showing exactly "Core / Non Core / Clear selection"; Location + Transaction Type = button name only on the 4 Aging/Unpaid Reports boards (11955:31802, 11955:32097, 11955:31901, 11955:32215); Invoice Status = button name only (11955:31458, 11955:31573); Type + User = button names only (QB Unexported); Mention = button name only (11982:9225 Notes). The only OPEN filter dropdowns in the entire file are the 19 Work-Order-page ones plus that single Parts board. None of the 6 is defined in spec v1.6 either (no S#-R# gives their options or behaviour).</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; on receipt, author per-type behavioural cases for the six with proper Rule-20 spec anchors; needs add_case authorization. B -&gt; record in the coverage-matrix that per-type behaviour for those six is deliberately covered at button-name/presence level only, by PO ruling, and raise each one as a follow-up as it is reached. The earlier "12 boards un-rendered, a behaviour board may still exist" caveat is now CLOSED - all 12 were accounted for on 2026-07-30 (7 read in full via the layer-tree endpoint, 5 already covered by extracted text) and there are ZERO Reports or Parts filter-behaviour boards in the file, so "maybe there is a board you have not seen" is no longer available as a deflection and this question can no longer self-resolve on a pending render (supersedes the earlier "may self-resolve" note).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>W1 - WITHDRAWN</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>FLT-URL-05 (C38879)
 FLT-URL-02 (C29618)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>WITHDRAWN - answered by spec v1.6 (S11-R6, added v1.4 / Confluence v9, 2026-07-27). Was Q1 of the 2026-07-30 sheet (= Questions-for-Branko-dev.md Q2 / deltas C1). VERBATIM: "Filter state arriving from a URL applies at runtime only. It never overwrites the user's saved filter state (S10-R2). Changes the user makes to filters while viewing a shared link are also not written back to their saved state: the entire visit is treated as a temporary view"</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Effective answer = option A (runtime-only; saved filters untouched; changes during the visit are not written back either). FLT-URL-05 already tests it clause-by-clause; only its refs/spec_ref are stale ('spec v1.3 export awaited') -&gt; re-point to S11-R6 (FIX-PLAN F4). Never sent to Branko.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>W2 - WITHDRAWN</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>FLT-STAT-07 (C38877)
 FLT-STAT-03 (C29562)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>WITHDRAWN - answered by spec v1.6 (S2-R7 + S2-N4, added v1.4 / Confluence v9, 2026-07-27). Was Q2 of the 2026-07-30 sheet (= Questions-for-Branko-dev.md Q3 / deltas C2). VERBATIM S2-R7: "Imported is an exception to S2-R2 and cannot be combined with anything else. Imported work orders come from a different data source rather than being a status of the existing records, so selecting Imported switches the list to the imported records and disables the other filter chips while it is active. Deselecting Imported returns the list and re-enables the other chips. This is current production behaviour and is unchanged by this work" | VERBATIM S2-N4: "Selecting Imported alongside another status, customer, technician, advisor or asset filter is not a supported combination and is prevented by S2-R7 rather than returning an empty result"</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Effective answer = option A (Imported works alone; other chips disabled while active; deselecting re-enables them). FLT-STAT-07 already covers S2-R7 + S2-N4 fully; only its refs/spec_ref + its 'PENDING BRANKO' note are stale (FIX-PLAN F3). Never sent to Branko.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>W3 - WITHDRAWN</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>FLT-URL-05 (C38879)
 FLT-URL-06 (new, no C-ID yet)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>WITHDRAWN - answered by spec v1.6 (S11-R7; CTA renamed in v1.5 / Confluence v10, 2026-07-27). Was the naming question INSIDE Q1 of the 2026-07-30 sheet ('a small "back to my saved filters" option'). VERBATIM: "While viewing filter state that arrived from a URL, a "Back to my view" action is available. It discards the shared view and restores the user's own saved filters. It also clears any active search query, because the query is not part of saved state and there is nothing to restore it to. The label is deliberately "my view" rather than "my filters", since the action affects both filters and search"</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Ratified label = 'Back to my view' (not 'back to my saved filters'). Use it in FLT-URL-05 per Rule 9 and add the untested 'it also clears any active search query' clause (FIX-PLAN F5); the negative S11-N3 ('not shown when viewing your own state') still needs a NEW case (FIX-PLAN F6). Never sent to Branko.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Already resolved - NOT asked</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>FLT-TAB-02 (C29609)
 FLT-TAB-03 (C29610)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Status chip on Estimates/Completed tabs (Questions-for-Branko-dev.md Q1 / delta C3) - RESOLVED by user ruling 2026-07-30: the tech plan's 'hidden' and Branko's earlier 'greyed-out/disabled' describe the SAME behavior. Note 2026-07-31: spec v1.6 still says 'hidden'/'not shown' in S9-R2, S9-R3, S2-N1, S2-N2, S1-N1 and section 4 Key Decisions - text unchanged since V1.0.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Cases stand as pushed - no case change, no TestRail write. The PRD-alignment ask for Branko is FIX-PLAN B1, deliberately NOT added to this sheet; it does not reopen the ruling.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Already resolved - NOT asked</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>FLT-SRCH-01..09 (no C-ids; none in TestRail)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Page-search 'spotlight/palette' ownership - already put to Branko as Question 6 of PO-Questions-Branko-PartsReports-2026-07-27.md ('The pop-up search box'); not duplicated here. SPEC-DIFF section 4 Group D is strong new evidence they are Global Search v2, not Filters Story 13.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Per user ruling 2026-07-31 the nine cases are NOT to be deleted unless Branko confirms Global-Search-only ownership. His answer decides move-vs-keep.</t>
         </is>

--- a/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
+++ b/build/filters/PO-Questions-Branko-Filters-TechPlan_2026-07-30.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions for PO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Internal Mapping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Questions for PO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QA Internal Mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,7 +755,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -786,9 +785,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>FLT-MOB-04 (C29624)
+          <t>7-case pattern (all C-ids re-verified against testrail-id-map.csv 2026-07-31):
 FLT-MOB-02 (C29622)
-FLT-MOB-03 (C29623)</t>
+FLT-MOB-03 (C29623)
+FLT-MOB-04 (C29624)  &lt;- the case originally flagged
+FLT-MOB-05 (C29625)
+FLT-MOB-06 (C29626)
+FLT-MOB-07 (C29627)
+FLT-MOB-08 (C29628)
+[COUNT WIDENED 3 -&gt; 7 on 2026-07-31 by the design reconciliation - design-2026-07-31/RECONCILIATION-12-2026-07-31.md B-1 ("it is not a lone case; it is a 7-case pattern") and RECONCILIATION-FINAL-2026-07-31.md B-1 (cases implicated, none changed: C29622-C29628). The earlier mapping listed only FLT-MOB-02/03/04 and was therefore narrower than reality: every one of the seven mobile cases asserts applying via an "Apply filter(s)" button, so Branko's answer moves all seven, not three.]</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -798,7 +803,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>A -&gt; reword FLT-MOB-04 to instant-apply, no button. B -&gt; case stands as designed (Apply button). Either way FLT-MOB-02/03 keep the combined-sheet Apply button (design 11884:13689 + D15 = IN) and all three get the same 'confirm live which pattern ships' note (FIX-PLAN F2). Verify LIVE at VIU.</t>
+          <t>A -&gt; reword FLT-MOB-04 to instant-apply, no button. B -&gt; case stands as designed (Apply button). Either way FLT-MOB-02/03/05/06/07/08 keep the combined-sheet Apply button (design 11884:13689 + D15 = IN) and all seven get the same 'confirm live which pattern ships' note (FIX-PLAN F2). Verify LIVE at VIU.</t>
         </is>
       </c>
     </row>
